--- a/data/file_generation/input/data_198/教师课程班级对应表_合并版.xlsx
+++ b/data/file_generation/input/data_198/教师课程班级对应表_合并版.xlsx
@@ -3660,18 +3660,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB6C8BC2-BA6E-4BE6-90EF-9F1A0D3AD983}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB206E64-1A64-4692-B785-205C296FD6AA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4926AC58-8A68-488D-A5FA-1F66CBCF30BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40FB54EA-949B-428E-9AEA-A5CB728C399B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3859B44B-F1E9-4F5B-BDB5-DC183CE08037}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5389555-74DB-4544-B702-AA37DF3BD6C1}"/>
 </file>